--- a/docs/Decodifiche/102_dec_stato_flusso_notifiche.xlsx
+++ b/docs/Decodifiche/102_dec_stato_flusso_notifiche.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
   <si>
     <t>ID</t>
   </si>
@@ -51,15 +51,6 @@
   </si>
   <si>
     <t>RIFIUTATA</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>STATOINFORMATIVO</t>
-  </si>
-  <si>
-    <t>2024-05-29 00:00:00.0</t>
   </si>
   <si>
     <t>10</t>
@@ -130,11 +121,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="3.265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="20.04296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="15.1484375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.33984375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.33984375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="15.55859375" customWidth="true" bestFit="true"/>
@@ -222,24 +213,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
